--- a/batteries.xlsx
+++ b/batteries.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\technicien_knx\Documents\Antoine_Collignon\Simulateur\Application\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\technicien_knx\Documents\GitHub\SimulationPV\App_Interne\Application_Interne\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB34F87-5EE5-4CE6-BB46-8337FE01568B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E428B9F9-4254-4912-9649-8BB26E8CF352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="165" windowWidth="29040" windowHeight="15720" xr2:uid="{439F2F0B-EBB6-48D7-BDE1-24F1D6BB5D52}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{439F2F0B-EBB6-48D7-BDE1-24F1D6BB5D52}"/>
   </bookViews>
   <sheets>
     <sheet name="Batt" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="47">
   <si>
     <t>Marque</t>
   </si>
@@ -163,6 +163,21 @@
   </si>
   <si>
     <t>Rendement</t>
+  </si>
+  <si>
+    <t>Pylontech</t>
+  </si>
+  <si>
+    <t>US5000-48V</t>
+  </si>
+  <si>
+    <t>US5000-48V 2x</t>
+  </si>
+  <si>
+    <t>US5000-48V 3x</t>
+  </si>
+  <si>
+    <t>US5000-48V 4x</t>
   </si>
 </sst>
 </file>
@@ -584,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38952B00-7C12-4340-981B-DAC64C55AA63}">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
@@ -1102,6 +1117,74 @@
       </c>
       <c r="G23">
         <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24">
+        <v>4.8</v>
+      </c>
+      <c r="D24">
+        <v>4.8</v>
+      </c>
+      <c r="E24">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25">
+        <v>9.6</v>
+      </c>
+      <c r="D25">
+        <v>9.6</v>
+      </c>
+      <c r="E25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26">
+        <v>14.4</v>
+      </c>
+      <c r="D26">
+        <v>14.4</v>
+      </c>
+      <c r="E26">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27">
+        <v>19.2</v>
+      </c>
+      <c r="D27">
+        <v>19.2</v>
+      </c>
+      <c r="E27">
+        <v>10.5</v>
       </c>
     </row>
   </sheetData>

--- a/batteries.xlsx
+++ b/batteries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\technicien_knx\Documents\GitHub\SimulationPV\App_Interne\Application_Interne\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E428B9F9-4254-4912-9649-8BB26E8CF352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{262D3093-AF8B-44F1-8838-393FCB66E32D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{439F2F0B-EBB6-48D7-BDE1-24F1D6BB5D52}"/>
   </bookViews>
@@ -1135,6 +1135,9 @@
       <c r="E24">
         <v>3.5</v>
       </c>
+      <c r="G24">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
@@ -1152,6 +1155,9 @@
       <c r="E25">
         <v>9</v>
       </c>
+      <c r="G25">
+        <v>9.6</v>
+      </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
@@ -1169,6 +1175,9 @@
       <c r="E26">
         <v>10.5</v>
       </c>
+      <c r="G26">
+        <v>14.4</v>
+      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
@@ -1185,6 +1194,9 @@
       </c>
       <c r="E27">
         <v>10.5</v>
+      </c>
+      <c r="G27">
+        <v>19.2</v>
       </c>
     </row>
   </sheetData>

--- a/batteries.xlsx
+++ b/batteries.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\technicien_knx\Documents\GitHub\SimulationPV\App_Interne\Application_Interne\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\technicien_knx\Documents\Antoine_Collignon\Simulateur\Application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{262D3093-AF8B-44F1-8838-393FCB66E32D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB34F87-5EE5-4CE6-BB46-8337FE01568B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{439F2F0B-EBB6-48D7-BDE1-24F1D6BB5D52}"/>
+    <workbookView xWindow="28680" yWindow="165" windowWidth="29040" windowHeight="15720" xr2:uid="{439F2F0B-EBB6-48D7-BDE1-24F1D6BB5D52}"/>
   </bookViews>
   <sheets>
     <sheet name="Batt" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="42">
   <si>
     <t>Marque</t>
   </si>
@@ -163,21 +163,6 @@
   </si>
   <si>
     <t>Rendement</t>
-  </si>
-  <si>
-    <t>Pylontech</t>
-  </si>
-  <si>
-    <t>US5000-48V</t>
-  </si>
-  <si>
-    <t>US5000-48V 2x</t>
-  </si>
-  <si>
-    <t>US5000-48V 3x</t>
-  </si>
-  <si>
-    <t>US5000-48V 4x</t>
   </si>
 </sst>
 </file>
@@ -599,7 +584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38952B00-7C12-4340-981B-DAC64C55AA63}">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
@@ -1117,86 +1102,6 @@
       </c>
       <c r="G23">
         <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24">
-        <v>4.8</v>
-      </c>
-      <c r="D24">
-        <v>4.8</v>
-      </c>
-      <c r="E24">
-        <v>3.5</v>
-      </c>
-      <c r="G24">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25">
-        <v>9.6</v>
-      </c>
-      <c r="D25">
-        <v>9.6</v>
-      </c>
-      <c r="E25">
-        <v>9</v>
-      </c>
-      <c r="G25">
-        <v>9.6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26">
-        <v>14.4</v>
-      </c>
-      <c r="D26">
-        <v>14.4</v>
-      </c>
-      <c r="E26">
-        <v>10.5</v>
-      </c>
-      <c r="G26">
-        <v>14.4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27">
-        <v>19.2</v>
-      </c>
-      <c r="D27">
-        <v>19.2</v>
-      </c>
-      <c r="E27">
-        <v>10.5</v>
-      </c>
-      <c r="G27">
-        <v>19.2</v>
       </c>
     </row>
   </sheetData>
